--- a/dataset_t6_grouped/results2/G4/G4_T6321_W0022F0002T0006Z000C1N35_analysis.xlsx
+++ b/dataset_t6_grouped/results2/G4/G4_T6321_W0022F0002T0006Z000C1N35_analysis.xlsx
@@ -480,16 +480,16 @@
         <v>1</v>
       </c>
       <c r="C2" t="n">
-        <v>17.45991481377847</v>
+        <v>2.837236157239001</v>
       </c>
       <c r="D2" t="n">
-        <v>17.79905398834192</v>
+        <v>2.892346273105562</v>
       </c>
       <c r="E2" t="n">
-        <v>13.62733839457076</v>
+        <v>2.214442489117749</v>
       </c>
       <c r="F2" t="n">
-        <v>13.40598565071897</v>
+        <v>2.178472668241833</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
@@ -512,16 +512,16 @@
         <v>2</v>
       </c>
       <c r="C3" t="n">
-        <v>53.88486813748197</v>
+        <v>8.75629107234082</v>
       </c>
       <c r="D3" t="n">
-        <v>53.62474913570344</v>
+        <v>8.714021734551809</v>
       </c>
       <c r="E3" t="n">
-        <v>13.62733839457076</v>
+        <v>2.214442489117749</v>
       </c>
       <c r="F3" t="n">
-        <v>13.40598565071897</v>
+        <v>2.178472668241833</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
@@ -544,16 +544,16 @@
         <v>3</v>
       </c>
       <c r="C4" t="n">
-        <v>43.90402517459817</v>
+        <v>7.134404090872204</v>
       </c>
       <c r="D4" t="n">
-        <v>43.67025171547701</v>
+        <v>7.096415903765014</v>
       </c>
       <c r="E4" t="n">
-        <v>13.62733839457076</v>
+        <v>2.214442489117749</v>
       </c>
       <c r="F4" t="n">
-        <v>13.40598565071897</v>
+        <v>2.178472668241833</v>
       </c>
       <c r="G4" t="inlineStr">
         <is>
@@ -576,16 +576,16 @@
         <v>4</v>
       </c>
       <c r="C5" t="n">
-        <v>31.6580053975814</v>
+        <v>5.144425877106978</v>
       </c>
       <c r="D5" t="n">
-        <v>31.54138852290108</v>
+        <v>5.125475634971425</v>
       </c>
       <c r="E5" t="n">
-        <v>13.62733839457076</v>
+        <v>2.214442489117749</v>
       </c>
       <c r="F5" t="n">
-        <v>13.40598565071897</v>
+        <v>2.178472668241833</v>
       </c>
       <c r="G5" t="inlineStr">
         <is>
